--- a/CONSUMO SEMANALES DE CAFÉ.xlsx
+++ b/CONSUMO SEMANALES DE CAFÉ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7829DF-A7F5-4366-9F77-A3F55839D531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC29BCAA-1213-4B2E-88A3-D7269D9B5361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,30 +32,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>PROMOS</t>
   </si>
@@ -96,18 +74,9 @@
     <t>kilos.</t>
   </si>
   <si>
-    <t>bolsas</t>
-  </si>
-  <si>
     <t>CORTADO</t>
   </si>
   <si>
-    <t>TOTAL UNIDADES</t>
-  </si>
-  <si>
-    <t>TOTAL KILOS</t>
-  </si>
-  <si>
     <t>2 CAFE CON LECHE</t>
   </si>
   <si>
@@ -142,13 +111,16 @@
   </si>
   <si>
     <t>AMERICANO</t>
+  </si>
+  <si>
+    <t>BOLSAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -180,20 +152,8 @@
       <name val="Amasis MT Pro Black"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="15"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Amasis MT Pro Black"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color rgb="FF000000"/>
-      <name val="Amasis MT Pro Black"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,12 +174,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF3F3F3"/>
         <bgColor rgb="FFF3F3F3"/>
       </patternFill>
@@ -228,12 +182,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF93C47D"/>
         <bgColor rgb="FF93C47D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -264,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -273,197 +221,32 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color rgb="FF000000"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00FF00"/>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color rgb="FF000000"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00FF00"/>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <font>
         <b val="0"/>
@@ -505,19 +288,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -557,19 +327,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -609,19 +366,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -647,19 +391,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -685,19 +416,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Amasis MT Pro Black"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -733,6 +451,142 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Amasis MT Pro Black"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Amasis MT Pro Black"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Amasis MT Pro Black"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Amasis MT Pro Black"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Amasis MT Pro Black"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Amasis MT Pro Black"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Amasis MT Pro Black"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Amasis MT Pro Black"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCDD9D4"/>
+          <bgColor rgb="FFCDD9D4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -753,14 +607,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFCDD9D4"/>
-          <bgColor rgb="FFCDD9D4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
           <bgColor rgb="FFF6F8F9"/>
         </patternFill>
@@ -838,50 +684,26 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="VENTAS DE CAFÉ-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="30"/>
-      <tableStyleElement type="headerRow" dxfId="33"/>
-      <tableStyleElement type="firstRowStripe" dxfId="32"/>
-      <tableStyleElement type="secondRowStripe" dxfId="31"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="27"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="firstRowStripe" dxfId="25"/>
+      <tableStyleElement type="secondRowStripe" dxfId="24"/>
     </tableStyle>
     <tableStyle name="DIVISIÓN-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="26"/>
-      <tableStyleElement type="headerRow" dxfId="29"/>
-      <tableStyleElement type="firstRowStripe" dxfId="28"/>
-      <tableStyleElement type="secondRowStripe" dxfId="27"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="23"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="secondRowStripe" dxfId="20"/>
     </tableStyle>
     <tableStyle name="CAFÉ-style" pivot="0" count="5" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="21"/>
-      <tableStyleElement type="headerRow" dxfId="25"/>
-      <tableStyleElement type="totalRow" dxfId="22"/>
-      <tableStyleElement type="firstRowStripe" dxfId="24"/>
-      <tableStyleElement type="secondRowStripe" dxfId="23"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="19"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="secondRowStripe" dxfId="15"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -896,21 +718,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DATOS" displayName="DATOS" ref="A2:I19" totalsRowCount="1" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="PROMOS" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="unidades" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="kilos" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doble" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="cantidad" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="kilos." dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="bolsas" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="TOTAL UNIDADES" totalsRowFunction="custom" dataDxfId="6" totalsRowDxfId="5">
-      <totalsRowFormula>SUM(DATOS[TOTAL UNIDADES])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="TOTAL KILOS" totalsRowFunction="custom" dataDxfId="4" totalsRowDxfId="3">
-      <totalsRowFormula array="1">SUM(DATOS[bolsas]+DATOS[TOTAL KILOS])</totalsRowFormula>
-    </tableColumn>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DATOS" displayName="DATOS" ref="A2:F19" totalsRowCount="1" headerRowDxfId="14" dataDxfId="13" totalsRowDxfId="12">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="PROMOS" dataDxfId="11" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="unidades" dataDxfId="10" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="kilos" dataDxfId="9" totalsRowDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="doble" dataDxfId="8" totalsRowDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="cantidad" dataDxfId="7" totalsRowDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="kilos." dataDxfId="6" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1117,7 +932,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
@@ -1125,516 +940,353 @@
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="22.77734375" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.88671875" style="2" customWidth="1"/>
-    <col min="6" max="7" width="20.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="2"/>
+    <col min="6" max="6" width="20.88671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>748</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <f t="shared" ref="C3:C17" si="0">((B3)*19)/1000</f>
         <v>14.212</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="6">
         <v>599</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="6">
         <f t="shared" ref="F3:F12" si="1">(E3*19)/1000</f>
         <v>11.381</v>
       </c>
-      <c r="G3" s="8">
-        <v>12</v>
-      </c>
-      <c r="H3" s="9">
-        <f t="shared" ref="H3:I3" si="2">SUM(B3,E3)</f>
-        <v>1347</v>
-      </c>
-      <c r="I3" s="9">
-        <f t="shared" si="2"/>
-        <v>25.593</v>
-      </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="8">
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6">
         <v>22</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <f t="shared" si="0"/>
         <v>0.41799999999999998</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="D4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6">
         <v>259</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <f t="shared" si="1"/>
         <v>4.9210000000000003</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9">
-        <f t="shared" ref="H4:I4" si="3">SUM(B4,E4)</f>
-        <v>281</v>
-      </c>
-      <c r="I4" s="9">
-        <f t="shared" si="3"/>
-        <v>5.3390000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    </row>
+    <row r="5" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>36</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <f t="shared" si="0"/>
         <v>0.68400000000000005</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="6">
         <v>2</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="6">
         <f t="shared" si="1"/>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="9">
-        <f t="shared" ref="H5:I5" si="4">SUM(B5,E5)</f>
-        <v>38</v>
-      </c>
-      <c r="I5" s="9">
-        <f t="shared" si="4"/>
-        <v>0.72200000000000009</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="8">
+    </row>
+    <row r="6" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6">
         <v>9</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <f t="shared" si="0"/>
         <v>0.17100000000000001</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6">
         <v>5</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <f t="shared" si="1"/>
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9">
-        <f t="shared" ref="H6:I6" si="5">SUM(B6,E6)</f>
-        <v>14</v>
-      </c>
-      <c r="I6" s="9">
-        <f t="shared" si="5"/>
-        <v>0.26600000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    </row>
+    <row r="7" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>9</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <f t="shared" si="0"/>
         <v>0.17100000000000001</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6">
         <v>5</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <f t="shared" si="1"/>
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9">
-        <f t="shared" ref="H7:I7" si="6">SUM(B7,E7)</f>
-        <v>14</v>
-      </c>
-      <c r="I7" s="9">
-        <f t="shared" si="6"/>
-        <v>0.26600000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8">
+    </row>
+    <row r="8" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6">
         <v>2</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <f t="shared" si="1"/>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9">
-        <f t="shared" ref="H8:I8" si="7">SUM(B8,E8)</f>
-        <v>2</v>
-      </c>
-      <c r="I8" s="9">
-        <f t="shared" si="7"/>
-        <v>3.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8">
+    </row>
+    <row r="9" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="D9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="6">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <f t="shared" si="1"/>
         <v>1.9E-2</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9">
-        <f t="shared" ref="H9:I9" si="8">SUM(B9,E9)</f>
-        <v>1</v>
-      </c>
-      <c r="I9" s="9">
-        <f t="shared" si="8"/>
-        <v>1.9E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8">
+    </row>
+    <row r="10" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="D10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="6">
         <v>20</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="6">
         <f t="shared" si="1"/>
         <v>0.38</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9">
-        <f t="shared" ref="H10:I10" si="9">SUM(B10,E10)</f>
-        <v>20</v>
-      </c>
-      <c r="I10" s="9">
-        <f t="shared" si="9"/>
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8">
+    </row>
+    <row r="11" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="D11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="6">
         <v>56</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="6">
         <f t="shared" si="1"/>
         <v>1.0640000000000001</v>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="9">
-        <f t="shared" ref="H11:I11" si="10">SUM(B11,E11)</f>
-        <v>56</v>
-      </c>
-      <c r="I11" s="9">
-        <f t="shared" si="10"/>
-        <v>1.0640000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8">
+    </row>
+    <row r="12" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="6">
         <v>33</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="6">
         <f t="shared" si="1"/>
         <v>0.627</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="9">
-        <f t="shared" ref="H12:I12" si="11">SUM(B12,E12)</f>
-        <v>33</v>
-      </c>
-      <c r="I12" s="9">
-        <f t="shared" si="11"/>
-        <v>0.627</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8">
+    </row>
+    <row r="13" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="D13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="6">
         <v>437</v>
       </c>
-      <c r="F13" s="8">
-        <f t="shared" ref="F13:F17" si="12">(E13*14)/1000</f>
+      <c r="F13" s="6">
+        <f t="shared" ref="F13:F17" si="2">(E13*14)/1000</f>
         <v>6.1180000000000003</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9">
-        <f t="shared" ref="H13:I13" si="13">SUM(B13,E13)</f>
-        <v>437</v>
-      </c>
-      <c r="I13" s="9">
-        <f t="shared" si="13"/>
-        <v>6.1180000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8">
+    </row>
+    <row r="14" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="D14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="6">
         <v>11</v>
       </c>
-      <c r="F14" s="8">
-        <f t="shared" si="12"/>
+      <c r="F14" s="6">
+        <f t="shared" si="2"/>
         <v>0.154</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="9">
-        <f t="shared" ref="H14:I14" si="14">SUM(B14,E14)</f>
-        <v>11</v>
-      </c>
-      <c r="I14" s="9">
-        <f t="shared" si="14"/>
-        <v>0.154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8">
+    </row>
+    <row r="15" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
         <v>14</v>
       </c>
-      <c r="F15" s="8">
-        <f t="shared" si="12"/>
+      <c r="F15" s="6">
+        <f t="shared" si="2"/>
         <v>0.19600000000000001</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9">
-        <f t="shared" ref="H15:I15" si="15">SUM(B15,E15)</f>
-        <v>14</v>
-      </c>
-      <c r="I15" s="9">
-        <f t="shared" si="15"/>
-        <v>0.19600000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8">
+    </row>
+    <row r="16" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="D16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="6">
         <v>2</v>
       </c>
-      <c r="F16" s="8">
-        <f t="shared" si="12"/>
+      <c r="F16" s="6">
+        <f t="shared" si="2"/>
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="9">
-        <f t="shared" ref="H16:I16" si="16">SUM(B16,E16)</f>
-        <v>2</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="16"/>
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8">
+    </row>
+    <row r="17" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="6">
         <v>1</v>
       </c>
-      <c r="F17" s="8">
-        <f t="shared" si="12"/>
+      <c r="F17" s="6">
+        <f t="shared" si="2"/>
         <v>1.4E-2</v>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="9">
-        <f t="shared" ref="H17:I17" si="17">SUM(B17,E17)</f>
-        <v>1</v>
-      </c>
-      <c r="I17" s="9">
-        <f t="shared" si="17"/>
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8">
+    </row>
+    <row r="18" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="6">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6">
+        <v>12</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6">
         <f>(E18*19)/1000</f>
         <v>0</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="9">
-        <f t="shared" ref="H18:I18" si="18">SUM(B18,E18)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
+    </row>
+    <row r="19" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="14">
-        <f>SUM(DATOS[TOTAL UNIDADES])</f>
-        <v>2271</v>
-      </c>
-      <c r="I19" s="14" cm="1">
-        <f t="array" ref="I19">SUM(DATOS[bolsas]+DATOS[TOTAL KILOS])</f>
-        <v>52.824000000000005</v>
-      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
